--- a/clustering/8 subclusters (VDS_r (costs_r) 1 prop IQR).xlsx
+++ b/clustering/8 subclusters (VDS_r (costs_r) 1 prop IQR).xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="9">
   <si>
     <t>clust</t>
   </si>
@@ -43,15 +43,6 @@
   </si>
   <si>
     <t>RDequip_r</t>
-  </si>
-  <si>
-    <t>ITcosts_s</t>
-  </si>
-  <si>
-    <t>skvozcosts_s</t>
-  </si>
-  <si>
-    <t>trainingcosts_s</t>
   </si>
   <si>
     <t>Медианы кластеров</t>
@@ -776,13 +767,13 @@
         <v>1</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -969,7 +960,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
